--- a/MainTop/10.09.2026 Макс Озон/print_print_sorted.xlsx
+++ b/MainTop/10.09.2026 Макс Озон/print_print_sorted.xlsx
@@ -2713,7 +2713,7 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         </is>
       </c>
       <c r="K55" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56">
